--- a/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,29 +652,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Caramel Apple Butter</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Monin - Caramel Apple Butter</t>
+          <t>Monin - White Chocolate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.00</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -682,34 +678,30 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Monin - Cookie Butter</t>
+          <t>PKT Salt</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>7.92</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>WEBSTAURANT</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Monin - Hazelnut</t>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -719,58 +711,66 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>49.99</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>49.99</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Monin - Lavender</t>
+          <t>Torani - Caramel Sauce</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Web/EC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8.75</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>17.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Monin - Orange</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -782,22 +782,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Monin - Peppermint</t>
+          <t>Torani - Pumpkin Pie Sauce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>36.50</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Monin - Toasted Marshmallow</t>
+          <t>Torani - White Chocolate Sauce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -815,20 +815,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H&amp;M</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Monin - Toffee Nut</t>
+          <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -838,12 +842,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>5.97</t>
         </is>
       </c>
     </row>
@@ -851,7 +855,7 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Monin - Vanilla Sugar Free</t>
+          <t>FRZ Fruit - Blueberry</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -861,12 +865,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>55.46</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>110.92</t>
         </is>
       </c>
     </row>
@@ -874,7 +878,7 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monin - White Chocolate</t>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -894,33 +898,41 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Grandma's</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PKT Salt</t>
+          <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>36.70</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Grandma's</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -930,24 +942,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>18.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>18.35</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Web/EC</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,81 +965,77 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>83.29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>83.29</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Web/EC</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Java Box (160oz)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>92.59</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>92.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>WEB</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.59</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Butter - Salted</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>18.25</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>36.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Torani - White Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -1044,14 +1048,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>H&amp;M</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
+          <t>Flour - Millers Choice</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Blueberry</t>
+          <t>Goat Cheese</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.46</t>
+          <t>147.04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>110.92</t>
+          <t>147.04</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
+          <t>Mustard - Honey</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1117,125 +1117,25 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Grandma's</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
+          <t>Nuts - Walnut Halves &amp; Pieces</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Grandma's</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>18.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Java Box (96oz)</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>83.29</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>83.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Java Box (160oz)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>92.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>4.59</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>9.18</t>
+          <t>3.08</t>
         </is>
       </c>
     </row>
